--- a/silbido-master/Analisi_no_fischi_no_rumore80%_200ms.xlsx
+++ b/silbido-master/Analisi_no_fischi_no_rumore80%_200ms.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="145" uniqueCount="65">
   <si>
     <t>file_name</t>
   </si>
@@ -115,6 +115,99 @@
   </si>
   <si>
     <t>06</t>
+  </si>
+  <si>
+    <t>5498.230414075410.wav</t>
+  </si>
+  <si>
+    <t>2023-04-14 07:54:10</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>5498.230414085410.wav</t>
+  </si>
+  <si>
+    <t>2023-04-14 08:54:10</t>
+  </si>
+  <si>
+    <t>5498.230414095410.wav</t>
+  </si>
+  <si>
+    <t>2023-04-14 09:54:10</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>5498.230414105410.wav</t>
+  </si>
+  <si>
+    <t>2023-04-14 10:54:10</t>
+  </si>
+  <si>
+    <t>5498.250616072504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 07:25:04</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>5498.250616082504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 08:25:04</t>
+  </si>
+  <si>
+    <t>5498.250616092504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 09:25:04</t>
+  </si>
+  <si>
+    <t>5498.250616102504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 10:25:04</t>
+  </si>
+  <si>
+    <t>5498.250616112504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 11:25:04</t>
+  </si>
+  <si>
+    <t>5498.250616122504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 12:25:04</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>5498.250616132504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 13:25:04</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>5498.250616142504.wav</t>
+  </si>
+  <si>
+    <t>2025-06-16 14:25:04</t>
   </si>
 </sst>
 </file>
@@ -160,7 +253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="true"/>
@@ -348,6 +441,354 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>